--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ74"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2356,50 +2356,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>67944007</v>
+        <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87289</v>
+        <v>87544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettrandad spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius pseudoglaucopus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>689887</v>
+        <v>689817</v>
       </c>
       <c r="R18" t="n">
-        <v>6371500</v>
+        <v>6371627</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2423,12 +2421,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,24 +2452,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944007</t>
+          <t>https://artportalen.se/Sighting/137252242</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67944445</v>
+        <v>67944007</v>
       </c>
       <c r="B19" t="n">
         <v>87289</v>
@@ -2498,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>689927</v>
+        <v>689887</v>
       </c>
       <c r="R19" t="n">
-        <v>6371620</v>
+        <v>6371500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,38 +2568,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944445</t>
+          <t>https://artportalen.se/Sighting/67944007</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67943929</v>
+        <v>67944445</v>
       </c>
       <c r="B20" t="n">
-        <v>91680</v>
+        <v>87289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>473</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2603,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>689918</v>
+        <v>689927</v>
       </c>
       <c r="R20" t="n">
-        <v>6371492</v>
+        <v>6371620</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,16 +2673,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943929</t>
+          <t>https://artportalen.se/Sighting/67944445</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67943973</v>
+        <v>67943929</v>
       </c>
       <c r="B21" t="n">
-        <v>87309</v>
+        <v>91680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,21 +2690,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2716,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>689904</v>
+        <v>689918</v>
       </c>
       <c r="R21" t="n">
-        <v>6371501</v>
+        <v>6371492</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,16 +2778,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943973</t>
+          <t>https://artportalen.se/Sighting/67943929</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67944029</v>
+        <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>87309</v>
+        <v>91921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,39 +2795,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>L.mafrids, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>689880</v>
+        <v>689873</v>
       </c>
       <c r="R22" t="n">
-        <v>6371495</v>
+        <v>6371644</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2843,12 +2852,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,24 +2883,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944029</t>
+          <t>https://artportalen.se/Sighting/137250773</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67944061</v>
+        <v>67943973</v>
       </c>
       <c r="B23" t="n">
         <v>87309</v>
@@ -2918,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>689869</v>
+        <v>689904</v>
       </c>
       <c r="R23" t="n">
-        <v>6371495</v>
+        <v>6371501</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,13 +2999,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944061</t>
+          <t>https://artportalen.se/Sighting/67943973</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67944091</v>
+        <v>67944029</v>
       </c>
       <c r="B24" t="n">
         <v>87309</v>
@@ -3023,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>689904</v>
+        <v>689880</v>
       </c>
       <c r="R24" t="n">
-        <v>6371549</v>
+        <v>6371495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,13 +3104,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944091</t>
+          <t>https://artportalen.se/Sighting/67944029</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67944303</v>
+        <v>67944061</v>
       </c>
       <c r="B25" t="n">
         <v>87309</v>
@@ -3128,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>689910</v>
+        <v>689869</v>
       </c>
       <c r="R25" t="n">
-        <v>6371578</v>
+        <v>6371495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3190,13 +3209,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944303</t>
+          <t>https://artportalen.se/Sighting/67944061</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67944455</v>
+        <v>67944091</v>
       </c>
       <c r="B26" t="n">
         <v>87309</v>
@@ -3233,10 +3252,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>689927</v>
+        <v>689904</v>
       </c>
       <c r="R26" t="n">
-        <v>6371620</v>
+        <v>6371549</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,13 +3314,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944455</t>
+          <t>https://artportalen.se/Sighting/67944091</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67944822</v>
+        <v>67944303</v>
       </c>
       <c r="B27" t="n">
         <v>87309</v>
@@ -3338,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>689926</v>
+        <v>689910</v>
       </c>
       <c r="R27" t="n">
-        <v>6371638</v>
+        <v>6371578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,13 +3419,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944822</t>
+          <t>https://artportalen.se/Sighting/67944303</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67946116</v>
+        <v>67944455</v>
       </c>
       <c r="B28" t="n">
         <v>87309</v>
@@ -3443,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>689910</v>
+        <v>689927</v>
       </c>
       <c r="R28" t="n">
-        <v>6371636</v>
+        <v>6371620</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,13 +3524,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67946116</t>
+          <t>https://artportalen.se/Sighting/67944455</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67946845</v>
+        <v>67944822</v>
       </c>
       <c r="B29" t="n">
         <v>87309</v>
@@ -3548,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>689899</v>
+        <v>689926</v>
       </c>
       <c r="R29" t="n">
-        <v>6371639</v>
+        <v>6371638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,13 +3629,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67946845</t>
+          <t>https://artportalen.se/Sighting/67944822</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67947059</v>
+        <v>67946116</v>
       </c>
       <c r="B30" t="n">
         <v>87309</v>
@@ -3653,10 +3672,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>689862</v>
+        <v>689910</v>
       </c>
       <c r="R30" t="n">
-        <v>6371574</v>
+        <v>6371636</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,13 +3734,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947059</t>
+          <t>https://artportalen.se/Sighting/67946116</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67947073</v>
+        <v>67946845</v>
       </c>
       <c r="B31" t="n">
         <v>87309</v>
@@ -3758,10 +3777,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>689835</v>
+        <v>689899</v>
       </c>
       <c r="R31" t="n">
-        <v>6371544</v>
+        <v>6371639</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,38 +3839,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947073</t>
+          <t>https://artportalen.se/Sighting/67946845</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67944044</v>
+        <v>67947059</v>
       </c>
       <c r="B32" t="n">
-        <v>87170</v>
+        <v>87309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3882,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>689875</v>
+        <v>689862</v>
       </c>
       <c r="R32" t="n">
-        <v>6371498</v>
+        <v>6371574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,38 +3944,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944044</t>
+          <t>https://artportalen.se/Sighting/67947059</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67944120</v>
+        <v>67947073</v>
       </c>
       <c r="B33" t="n">
-        <v>87170</v>
+        <v>87309</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3968,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>689939</v>
+        <v>689835</v>
       </c>
       <c r="R33" t="n">
-        <v>6371567</v>
+        <v>6371544</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,56 +4049,57 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944120</t>
+          <t>https://artportalen.se/Sighting/67947073</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67944216</v>
+        <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87170</v>
+        <v>87519</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>L.mafrids, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>689938</v>
+        <v>689916</v>
       </c>
       <c r="R34" t="n">
-        <v>6371616</v>
+        <v>6371603</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4103,12 +4123,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4124,67 +4154,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944216</t>
+          <t>https://artportalen.se/Sighting/137250774</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67944257</v>
+        <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87170</v>
+        <v>87519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>689916</v>
+        <v>689866</v>
       </c>
       <c r="R35" t="n">
-        <v>6371608</v>
+        <v>6371511</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4208,12 +4236,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4222,74 +4260,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944257</t>
+          <t>https://artportalen.se/Sighting/137252239</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67944310</v>
+        <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87170</v>
+        <v>87519</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>689910</v>
+        <v>689971</v>
       </c>
       <c r="R36" t="n">
-        <v>6371578</v>
+        <v>6371612</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4313,12 +4348,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4327,31 +4372,30 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944310</t>
+          <t>https://artportalen.se/Sighting/137253832</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>67944386</v>
+        <v>67944044</v>
       </c>
       <c r="B37" t="n">
         <v>87170</v>
@@ -4388,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>689903</v>
+        <v>689875</v>
       </c>
       <c r="R37" t="n">
-        <v>6371624</v>
+        <v>6371498</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4450,13 +4494,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944386</t>
+          <t>https://artportalen.se/Sighting/67944044</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67944451</v>
+        <v>67944120</v>
       </c>
       <c r="B38" t="n">
         <v>87170</v>
@@ -4493,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>689927</v>
+        <v>689939</v>
       </c>
       <c r="R38" t="n">
-        <v>6371620</v>
+        <v>6371567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4555,13 +4599,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944451</t>
+          <t>https://artportalen.se/Sighting/67944120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67944927</v>
+        <v>67944216</v>
       </c>
       <c r="B39" t="n">
         <v>87170</v>
@@ -4598,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>689926</v>
+        <v>689938</v>
       </c>
       <c r="R39" t="n">
-        <v>6371638</v>
+        <v>6371616</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4660,13 +4704,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944927</t>
+          <t>https://artportalen.se/Sighting/67944216</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67947169</v>
+        <v>67944257</v>
       </c>
       <c r="B40" t="n">
         <v>87170</v>
@@ -4703,10 +4747,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>689758</v>
+        <v>689916</v>
       </c>
       <c r="R40" t="n">
-        <v>6371671</v>
+        <v>6371608</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4765,13 +4809,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947169</t>
+          <t>https://artportalen.se/Sighting/67944257</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67947197</v>
+        <v>67944310</v>
       </c>
       <c r="B41" t="n">
         <v>87170</v>
@@ -4808,10 +4852,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>689681</v>
+        <v>689910</v>
       </c>
       <c r="R41" t="n">
-        <v>6371801</v>
+        <v>6371578</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,38 +4914,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947197</t>
+          <t>https://artportalen.se/Sighting/67944310</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67944013</v>
+        <v>67944386</v>
       </c>
       <c r="B42" t="n">
-        <v>87146</v>
+        <v>87170</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4913,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>689887</v>
+        <v>689903</v>
       </c>
       <c r="R42" t="n">
-        <v>6371500</v>
+        <v>6371624</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4975,38 +5019,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944013</t>
+          <t>https://artportalen.se/Sighting/67944386</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>67944753</v>
+        <v>67944451</v>
       </c>
       <c r="B43" t="n">
-        <v>87146</v>
+        <v>87170</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5018,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>689926</v>
+        <v>689927</v>
       </c>
       <c r="R43" t="n">
-        <v>6371638</v>
+        <v>6371620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5080,38 +5124,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944753</t>
+          <t>https://artportalen.se/Sighting/67944451</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67947130</v>
+        <v>67944927</v>
       </c>
       <c r="B44" t="n">
-        <v>87146</v>
+        <v>87170</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5123,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>689865</v>
+        <v>689926</v>
       </c>
       <c r="R44" t="n">
-        <v>6371648</v>
+        <v>6371638</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5185,38 +5229,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947130</t>
+          <t>https://artportalen.se/Sighting/67944927</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67947218</v>
+        <v>67947169</v>
       </c>
       <c r="B45" t="n">
-        <v>87146</v>
+        <v>87170</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5228,10 +5272,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>689661</v>
+        <v>689758</v>
       </c>
       <c r="R45" t="n">
-        <v>6371812</v>
+        <v>6371671</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5290,38 +5334,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947218</t>
+          <t>https://artportalen.se/Sighting/67947169</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67944214</v>
+        <v>67947197</v>
       </c>
       <c r="B46" t="n">
-        <v>87204</v>
+        <v>87170</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248952</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5377,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>689938</v>
+        <v>689681</v>
       </c>
       <c r="R46" t="n">
-        <v>6371616</v>
+        <v>6371801</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,53 +5439,51 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944214</t>
+          <t>https://artportalen.se/Sighting/67947197</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67945670</v>
+        <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87204</v>
+        <v>87380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248952</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>689926</v>
+        <v>689931</v>
       </c>
       <c r="R47" t="n">
-        <v>6371638</v>
+        <v>6371558</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5468,12 +5510,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5482,74 +5534,71 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67945670</t>
+          <t>https://artportalen.se/Sighting/137250828</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>67943953</v>
+        <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87291</v>
+        <v>87380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>248955</v>
+        <v>3712</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>689906</v>
+        <v>689909</v>
       </c>
       <c r="R48" t="n">
-        <v>6371473</v>
+        <v>6371599</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5573,12 +5622,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5587,74 +5646,71 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943953</t>
+          <t>https://artportalen.se/Sighting/137250830</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67944238</v>
+        <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87291</v>
+        <v>87380</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>248955</v>
+        <v>3712</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>689926</v>
+        <v>689917</v>
       </c>
       <c r="R49" t="n">
         <v>6371609</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5678,12 +5734,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5692,74 +5758,71 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944238</t>
+          <t>https://artportalen.se/Sighting/137250832</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>67944354</v>
+        <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87291</v>
+        <v>87380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>248955</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>689901</v>
+        <v>689916</v>
       </c>
       <c r="R50" t="n">
-        <v>6371607</v>
+        <v>6371627</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5783,12 +5846,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5797,74 +5870,71 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944354</t>
+          <t>https://artportalen.se/Sighting/137250834</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>67944393</v>
+        <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87291</v>
+        <v>87380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>248955</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>689903</v>
+        <v>689981</v>
       </c>
       <c r="R51" t="n">
-        <v>6371624</v>
+        <v>6371574</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5888,12 +5958,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5902,74 +5982,71 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944393</t>
+          <t>https://artportalen.se/Sighting/137253830</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>67944041</v>
+        <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87262</v>
+        <v>87380</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>689875</v>
+        <v>689978</v>
       </c>
       <c r="R52" t="n">
-        <v>6371498</v>
+        <v>6371578</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5993,12 +6070,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6007,74 +6094,71 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944041</t>
+          <t>https://artportalen.se/Sighting/137253831</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67944249</v>
+        <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87262</v>
+        <v>87380</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>689920</v>
+        <v>689917</v>
       </c>
       <c r="R53" t="n">
-        <v>6371608</v>
+        <v>6371621</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6098,12 +6182,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6112,56 +6206,55 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944249</t>
+          <t>https://artportalen.se/Sighting/137253837</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67944366</v>
+        <v>67944013</v>
       </c>
       <c r="B54" t="n">
-        <v>87262</v>
+        <v>87146</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6173,10 +6266,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>689904</v>
+        <v>689887</v>
       </c>
       <c r="R54" t="n">
-        <v>6371615</v>
+        <v>6371500</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6235,38 +6328,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944366</t>
+          <t>https://artportalen.se/Sighting/67944013</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>67944426</v>
+        <v>67944753</v>
       </c>
       <c r="B55" t="n">
-        <v>87262</v>
+        <v>87146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6278,10 +6371,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>689917</v>
+        <v>689926</v>
       </c>
       <c r="R55" t="n">
-        <v>6371625</v>
+        <v>6371638</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6340,38 +6433,38 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944426</t>
+          <t>https://artportalen.se/Sighting/67944753</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>67944435</v>
+        <v>67947130</v>
       </c>
       <c r="B56" t="n">
-        <v>87262</v>
+        <v>87146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6383,10 +6476,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>689923</v>
+        <v>689865</v>
       </c>
       <c r="R56" t="n">
-        <v>6371614</v>
+        <v>6371648</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6445,38 +6538,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944435</t>
+          <t>https://artportalen.se/Sighting/67947130</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>67944468</v>
+        <v>67947218</v>
       </c>
       <c r="B57" t="n">
-        <v>87262</v>
+        <v>87146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6488,10 +6581,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>689939</v>
+        <v>689661</v>
       </c>
       <c r="R57" t="n">
-        <v>6371634</v>
+        <v>6371812</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6550,56 +6643,54 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944468</t>
+          <t>https://artportalen.se/Sighting/67947218</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>67946224</v>
+        <v>137250829</v>
       </c>
       <c r="B58" t="n">
-        <v>87262</v>
+        <v>90882</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>689910</v>
+        <v>689930</v>
       </c>
       <c r="R58" t="n">
-        <v>6371636</v>
+        <v>6371566</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6623,12 +6714,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6644,27 +6745,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67946224</t>
+          <t>https://artportalen.se/Sighting/137250829</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>67946776</v>
+        <v>137250833</v>
       </c>
       <c r="B59" t="n">
-        <v>87262</v>
+        <v>87579</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6672,39 +6773,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>689899</v>
+        <v>689917</v>
       </c>
       <c r="R59" t="n">
-        <v>6371639</v>
+        <v>6371609</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6728,12 +6827,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6742,34 +6851,33 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67946776</t>
+          <t>https://artportalen.se/Sighting/137250833</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>67947043</v>
+        <v>67944214</v>
       </c>
       <c r="B60" t="n">
-        <v>87262</v>
+        <v>87204</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6777,21 +6885,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248956</v>
+        <v>248952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6803,10 +6911,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>689900</v>
+        <v>689938</v>
       </c>
       <c r="R60" t="n">
-        <v>6371652</v>
+        <v>6371616</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6865,16 +6973,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947043</t>
+          <t>https://artportalen.se/Sighting/67944214</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>67947098</v>
+        <v>67945670</v>
       </c>
       <c r="B61" t="n">
-        <v>87262</v>
+        <v>87204</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6882,21 +6990,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248956</v>
+        <v>248952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6908,10 +7016,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>689859</v>
+        <v>689926</v>
       </c>
       <c r="R61" t="n">
-        <v>6371604</v>
+        <v>6371638</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6970,16 +7078,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947098</t>
+          <t>https://artportalen.se/Sighting/67945670</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>67947209</v>
+        <v>67943953</v>
       </c>
       <c r="B62" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6987,21 +7095,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7013,10 +7121,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>689674</v>
+        <v>689906</v>
       </c>
       <c r="R62" t="n">
-        <v>6371794</v>
+        <v>6371473</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7075,38 +7183,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947209</t>
+          <t>https://artportalen.se/Sighting/67943953</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67943938</v>
+        <v>67944238</v>
       </c>
       <c r="B63" t="n">
-        <v>87346</v>
+        <v>87291</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>248955</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7118,10 +7226,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>689918</v>
+        <v>689926</v>
       </c>
       <c r="R63" t="n">
-        <v>6371492</v>
+        <v>6371609</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7180,38 +7288,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943938</t>
+          <t>https://artportalen.se/Sighting/67944238</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67943995</v>
+        <v>67944354</v>
       </c>
       <c r="B64" t="n">
-        <v>87346</v>
+        <v>87291</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>248955</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7223,10 +7331,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>689894</v>
+        <v>689901</v>
       </c>
       <c r="R64" t="n">
-        <v>6371499</v>
+        <v>6371607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7285,38 +7393,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943995</t>
+          <t>https://artportalen.se/Sighting/67944354</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67944077</v>
+        <v>67944393</v>
       </c>
       <c r="B65" t="n">
-        <v>87346</v>
+        <v>87291</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>248955</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7328,10 +7436,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>689885</v>
+        <v>689903</v>
       </c>
       <c r="R65" t="n">
-        <v>6371516</v>
+        <v>6371624</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7390,38 +7498,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944077</t>
+          <t>https://artportalen.se/Sighting/67944393</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67944085</v>
+        <v>67944041</v>
       </c>
       <c r="B66" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7433,10 +7541,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>689904</v>
+        <v>689875</v>
       </c>
       <c r="R66" t="n">
-        <v>6371549</v>
+        <v>6371498</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,38 +7603,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944085</t>
+          <t>https://artportalen.se/Sighting/67944041</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67944104</v>
+        <v>67944249</v>
       </c>
       <c r="B67" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7538,10 +7646,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>689947</v>
+        <v>689920</v>
       </c>
       <c r="R67" t="n">
-        <v>6371552</v>
+        <v>6371608</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7600,38 +7708,38 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944104</t>
+          <t>https://artportalen.se/Sighting/67944249</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67944132</v>
+        <v>67944366</v>
       </c>
       <c r="B68" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7643,10 +7751,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>689923</v>
+        <v>689904</v>
       </c>
       <c r="R68" t="n">
-        <v>6371580</v>
+        <v>6371615</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7705,38 +7813,38 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944132</t>
+          <t>https://artportalen.se/Sighting/67944366</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>67944195</v>
+        <v>67944426</v>
       </c>
       <c r="B69" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7748,10 +7856,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>689957</v>
+        <v>689917</v>
       </c>
       <c r="R69" t="n">
-        <v>6371614</v>
+        <v>6371625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,38 +7918,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944195</t>
+          <t>https://artportalen.se/Sighting/67944426</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>67944328</v>
+        <v>67944435</v>
       </c>
       <c r="B70" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7853,10 +7961,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>689884</v>
+        <v>689923</v>
       </c>
       <c r="R70" t="n">
-        <v>6371592</v>
+        <v>6371614</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7915,38 +8023,38 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944328</t>
+          <t>https://artportalen.se/Sighting/67944435</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67944461</v>
+        <v>67944468</v>
       </c>
       <c r="B71" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7958,10 +8066,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>689927</v>
+        <v>689939</v>
       </c>
       <c r="R71" t="n">
-        <v>6371620</v>
+        <v>6371634</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8020,38 +8128,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944461</t>
+          <t>https://artportalen.se/Sighting/67944468</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>67945982</v>
+        <v>67946224</v>
       </c>
       <c r="B72" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8125,38 +8233,38 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67945982</t>
+          <t>https://artportalen.se/Sighting/67946224</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67947062</v>
+        <v>67946776</v>
       </c>
       <c r="B73" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8168,10 +8276,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>689862</v>
+        <v>689899</v>
       </c>
       <c r="R73" t="n">
-        <v>6371574</v>
+        <v>6371639</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8230,38 +8338,38 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947062</t>
+          <t>https://artportalen.se/Sighting/67946776</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>67947149</v>
+        <v>67947043</v>
       </c>
       <c r="B74" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8273,10 +8381,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>689810</v>
+        <v>689900</v>
       </c>
       <c r="R74" t="n">
-        <v>6371685</v>
+        <v>6371652</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8335,7 +8443,3062 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/67947043</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>67947098</v>
+      </c>
+      <c r="B75" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>689859</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6371604</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947098</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>67947209</v>
+      </c>
+      <c r="B76" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>689674</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6371794</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947209</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137250771</v>
+      </c>
+      <c r="B77" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>L.mafrids, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>689928</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6371602</v>
+      </c>
+      <c r="S77" t="n">
+        <v>6</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250771</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137250831</v>
+      </c>
+      <c r="B78" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>689909</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6371600</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250831</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137252243</v>
+      </c>
+      <c r="B79" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>689681</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6371784</v>
+      </c>
+      <c r="S79" t="n">
+        <v>24</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137252243</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>67943938</v>
+      </c>
+      <c r="B80" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>689918</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6371492</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943938</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>67943995</v>
+      </c>
+      <c r="B81" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>689894</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6371499</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943995</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>67944077</v>
+      </c>
+      <c r="B82" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>689885</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6371516</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944077</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>67944085</v>
+      </c>
+      <c r="B83" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>689904</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6371549</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944085</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>67944104</v>
+      </c>
+      <c r="B84" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>689947</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6371552</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944104</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>67944132</v>
+      </c>
+      <c r="B85" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>689923</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6371580</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944132</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>67944195</v>
+      </c>
+      <c r="B86" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>689957</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6371614</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944195</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>67944328</v>
+      </c>
+      <c r="B87" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>689884</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6371592</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944328</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>67944461</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>689927</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6371620</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944461</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>67945982</v>
+      </c>
+      <c r="B89" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>689910</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6371636</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67945982</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>67947062</v>
+      </c>
+      <c r="B90" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>689862</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6371574</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947062</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>67947149</v>
+      </c>
+      <c r="B91" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>689810</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6371685</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ingrid Thomasson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/67947149</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>137250770</v>
+      </c>
+      <c r="B92" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>L.mafrids, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>689930</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6371559</v>
+      </c>
+      <c r="S92" t="n">
+        <v>7</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250770</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>137250772</v>
+      </c>
+      <c r="B93" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>L.mafrids, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>689890</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6371658</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250772</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>137250835</v>
+      </c>
+      <c r="B94" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>689788</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6371728</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250835</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>137252240</v>
+      </c>
+      <c r="B95" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>689870</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6371553</v>
+      </c>
+      <c r="S95" t="n">
+        <v>16</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137252240</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>137252241</v>
+      </c>
+      <c r="B96" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>689850</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6371581</v>
+      </c>
+      <c r="S96" t="n">
+        <v>33</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137252241</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>137252244</v>
+      </c>
+      <c r="B97" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>689707</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6371692</v>
+      </c>
+      <c r="S97" t="n">
+        <v>17</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137252244</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>137252245</v>
+      </c>
+      <c r="B98" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Mosshagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>689816</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6371621</v>
+      </c>
+      <c r="S98" t="n">
+        <v>41</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137252245</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>137253829</v>
+      </c>
+      <c r="B99" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>689998</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6371544</v>
+      </c>
+      <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137253829</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>137253833</v>
+      </c>
+      <c r="B100" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>689970</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6371614</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137253833</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>137253835</v>
+      </c>
+      <c r="B101" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>689937</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6371596</v>
+      </c>
+      <c r="S101" t="n">
+        <v>12</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137253835</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>137253839</v>
+      </c>
+      <c r="B102" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>689918</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6371587</v>
+      </c>
+      <c r="S102" t="n">
+        <v>6</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137253839</t>
         </is>
       </c>
     </row>
@@ -8414,6 +11577,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6229,50 +6229,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67944013</v>
+        <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87146</v>
+        <v>87383</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>689887</v>
+        <v>689955</v>
       </c>
       <c r="R54" t="n">
-        <v>6371500</v>
+        <v>6371611</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6296,12 +6294,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6310,74 +6318,71 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944013</t>
+          <t>https://artportalen.se/Sighting/137273810</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>67944753</v>
+        <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87146</v>
+        <v>87383</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>689926</v>
+        <v>689919</v>
       </c>
       <c r="R55" t="n">
-        <v>6371638</v>
+        <v>6371633</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6401,12 +6406,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,31 +6430,30 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944753</t>
+          <t>https://artportalen.se/Sighting/137273811</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>67947130</v>
+        <v>67944013</v>
       </c>
       <c r="B56" t="n">
         <v>87146</v>
@@ -6476,10 +6490,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>689865</v>
+        <v>689887</v>
       </c>
       <c r="R56" t="n">
-        <v>6371648</v>
+        <v>6371500</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6538,13 +6552,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947130</t>
+          <t>https://artportalen.se/Sighting/67944013</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>67947218</v>
+        <v>67944753</v>
       </c>
       <c r="B57" t="n">
         <v>87146</v>
@@ -6581,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>689661</v>
+        <v>689926</v>
       </c>
       <c r="R57" t="n">
-        <v>6371812</v>
+        <v>6371638</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,16 +6657,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947218</t>
+          <t>https://artportalen.se/Sighting/67944753</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137250829</v>
+        <v>67947130</v>
       </c>
       <c r="B58" t="n">
-        <v>90882</v>
+        <v>87146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6660,37 +6674,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>245042</v>
+        <v>3762</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västergarn, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>689930</v>
+        <v>689865</v>
       </c>
       <c r="R58" t="n">
-        <v>6371566</v>
+        <v>6371648</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6714,22 +6730,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6745,65 +6751,67 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250829</t>
+          <t>https://artportalen.se/Sighting/67947130</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137250833</v>
+        <v>67947218</v>
       </c>
       <c r="B59" t="n">
-        <v>87579</v>
+        <v>87146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västergarn, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>689917</v>
+        <v>689661</v>
       </c>
       <c r="R59" t="n">
-        <v>6371609</v>
+        <v>6371812</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6827,22 +6835,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6851,73 +6849,72 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250833</t>
+          <t>https://artportalen.se/Sighting/67947218</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>67944214</v>
+        <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>87204</v>
+        <v>90882</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248952</v>
+        <v>245042</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>689938</v>
+        <v>689930</v>
       </c>
       <c r="R60" t="n">
-        <v>6371616</v>
+        <v>6371566</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6941,12 +6938,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6962,27 +6969,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944214</t>
+          <t>https://artportalen.se/Sighting/137250829</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>67945670</v>
+        <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87204</v>
+        <v>87579</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6990,39 +6997,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248952</v>
+        <v>248947</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>689926</v>
+        <v>689917</v>
       </c>
       <c r="R61" t="n">
-        <v>6371638</v>
+        <v>6371609</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7046,12 +7051,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7060,34 +7075,33 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67945670</t>
+          <t>https://artportalen.se/Sighting/137250833</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>67943953</v>
+        <v>67944214</v>
       </c>
       <c r="B62" t="n">
-        <v>87291</v>
+        <v>87204</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7095,21 +7109,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248955</v>
+        <v>248952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7121,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>689906</v>
+        <v>689938</v>
       </c>
       <c r="R62" t="n">
-        <v>6371473</v>
+        <v>6371616</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7183,16 +7197,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943953</t>
+          <t>https://artportalen.se/Sighting/67944214</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67944238</v>
+        <v>67945670</v>
       </c>
       <c r="B63" t="n">
-        <v>87291</v>
+        <v>87204</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7200,21 +7214,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>248955</v>
+        <v>248952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7229,7 +7243,7 @@
         <v>689926</v>
       </c>
       <c r="R63" t="n">
-        <v>6371609</v>
+        <v>6371638</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7288,13 +7302,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944238</t>
+          <t>https://artportalen.se/Sighting/67945670</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67944354</v>
+        <v>67943953</v>
       </c>
       <c r="B64" t="n">
         <v>87291</v>
@@ -7331,10 +7345,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>689901</v>
+        <v>689906</v>
       </c>
       <c r="R64" t="n">
-        <v>6371607</v>
+        <v>6371473</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7393,13 +7407,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944354</t>
+          <t>https://artportalen.se/Sighting/67943953</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67944393</v>
+        <v>67944238</v>
       </c>
       <c r="B65" t="n">
         <v>87291</v>
@@ -7436,10 +7450,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>689903</v>
+        <v>689926</v>
       </c>
       <c r="R65" t="n">
-        <v>6371624</v>
+        <v>6371609</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7498,16 +7512,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944393</t>
+          <t>https://artportalen.se/Sighting/67944238</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67944041</v>
+        <v>67944354</v>
       </c>
       <c r="B66" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7515,21 +7529,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7541,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>689875</v>
+        <v>689901</v>
       </c>
       <c r="R66" t="n">
-        <v>6371498</v>
+        <v>6371607</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7603,16 +7617,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944041</t>
+          <t>https://artportalen.se/Sighting/67944354</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67944249</v>
+        <v>67944393</v>
       </c>
       <c r="B67" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7620,21 +7634,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7646,10 +7660,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>689920</v>
+        <v>689903</v>
       </c>
       <c r="R67" t="n">
-        <v>6371608</v>
+        <v>6371624</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7708,13 +7722,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944249</t>
+          <t>https://artportalen.se/Sighting/67944393</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67944366</v>
+        <v>67944041</v>
       </c>
       <c r="B68" t="n">
         <v>87262</v>
@@ -7751,10 +7765,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>689904</v>
+        <v>689875</v>
       </c>
       <c r="R68" t="n">
-        <v>6371615</v>
+        <v>6371498</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7813,13 +7827,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944366</t>
+          <t>https://artportalen.se/Sighting/67944041</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>67944426</v>
+        <v>67944249</v>
       </c>
       <c r="B69" t="n">
         <v>87262</v>
@@ -7856,10 +7870,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>689917</v>
+        <v>689920</v>
       </c>
       <c r="R69" t="n">
-        <v>6371625</v>
+        <v>6371608</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7918,13 +7932,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944426</t>
+          <t>https://artportalen.se/Sighting/67944249</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>67944435</v>
+        <v>67944366</v>
       </c>
       <c r="B70" t="n">
         <v>87262</v>
@@ -7961,10 +7975,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>689923</v>
+        <v>689904</v>
       </c>
       <c r="R70" t="n">
-        <v>6371614</v>
+        <v>6371615</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8023,13 +8037,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944435</t>
+          <t>https://artportalen.se/Sighting/67944366</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67944468</v>
+        <v>67944426</v>
       </c>
       <c r="B71" t="n">
         <v>87262</v>
@@ -8066,10 +8080,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>689939</v>
+        <v>689917</v>
       </c>
       <c r="R71" t="n">
-        <v>6371634</v>
+        <v>6371625</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8128,13 +8142,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944468</t>
+          <t>https://artportalen.se/Sighting/67944426</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>67946224</v>
+        <v>67944435</v>
       </c>
       <c r="B72" t="n">
         <v>87262</v>
@@ -8171,10 +8185,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>689910</v>
+        <v>689923</v>
       </c>
       <c r="R72" t="n">
-        <v>6371636</v>
+        <v>6371614</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8233,13 +8247,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67946224</t>
+          <t>https://artportalen.se/Sighting/67944435</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67946776</v>
+        <v>67944468</v>
       </c>
       <c r="B73" t="n">
         <v>87262</v>
@@ -8276,10 +8290,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>689899</v>
+        <v>689939</v>
       </c>
       <c r="R73" t="n">
-        <v>6371639</v>
+        <v>6371634</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8338,13 +8352,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67946776</t>
+          <t>https://artportalen.se/Sighting/67944468</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>67947043</v>
+        <v>67946224</v>
       </c>
       <c r="B74" t="n">
         <v>87262</v>
@@ -8381,10 +8395,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>689900</v>
+        <v>689910</v>
       </c>
       <c r="R74" t="n">
-        <v>6371652</v>
+        <v>6371636</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8443,13 +8457,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947043</t>
+          <t>https://artportalen.se/Sighting/67946224</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>67947098</v>
+        <v>67946776</v>
       </c>
       <c r="B75" t="n">
         <v>87262</v>
@@ -8486,10 +8500,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>689859</v>
+        <v>689899</v>
       </c>
       <c r="R75" t="n">
-        <v>6371604</v>
+        <v>6371639</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8548,13 +8562,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947098</t>
+          <t>https://artportalen.se/Sighting/67946776</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>67947209</v>
+        <v>67947043</v>
       </c>
       <c r="B76" t="n">
         <v>87262</v>
@@ -8591,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>689674</v>
+        <v>689900</v>
       </c>
       <c r="R76" t="n">
-        <v>6371794</v>
+        <v>6371652</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8653,16 +8667,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947209</t>
+          <t>https://artportalen.se/Sighting/67947043</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137250771</v>
+        <v>67947098</v>
       </c>
       <c r="B77" t="n">
-        <v>87472</v>
+        <v>87262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8690,20 +8704,19 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>L.mafrids, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>689928</v>
+        <v>689859</v>
       </c>
       <c r="R77" t="n">
-        <v>6371602</v>
+        <v>6371604</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8727,22 +8740,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8758,27 +8761,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250771</t>
+          <t>https://artportalen.se/Sighting/67947098</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137250831</v>
+        <v>67947209</v>
       </c>
       <c r="B78" t="n">
-        <v>87472</v>
+        <v>87262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8804,19 +8807,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västergarn, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>689909</v>
+        <v>689674</v>
       </c>
       <c r="R78" t="n">
-        <v>6371600</v>
+        <v>6371794</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8840,22 +8845,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8864,30 +8859,31 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250831</t>
+          <t>https://artportalen.se/Sighting/67947209</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137252243</v>
+        <v>137250771</v>
       </c>
       <c r="B79" t="n">
         <v>87472</v>
@@ -8916,19 +8912,22 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>L.mafrids, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>689681</v>
+        <v>689928</v>
       </c>
       <c r="R79" t="n">
-        <v>6371784</v>
+        <v>6371602</v>
       </c>
       <c r="S79" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8957,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8967,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8976,73 +8975,72 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137252243</t>
+          <t>https://artportalen.se/Sighting/137250771</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>67943938</v>
+        <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87346</v>
+        <v>87472</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>689918</v>
+        <v>689909</v>
       </c>
       <c r="R80" t="n">
-        <v>6371492</v>
+        <v>6371600</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9066,12 +9064,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9080,74 +9088,71 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943938</t>
+          <t>https://artportalen.se/Sighting/137250831</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>67943995</v>
+        <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87346</v>
+        <v>87472</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>689894</v>
+        <v>689681</v>
       </c>
       <c r="R81" t="n">
-        <v>6371499</v>
+        <v>6371784</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9171,12 +9176,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9185,31 +9200,30 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67943995</t>
+          <t>https://artportalen.se/Sighting/137252243</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>67944077</v>
+        <v>67943938</v>
       </c>
       <c r="B82" t="n">
         <v>87346</v>
@@ -9246,10 +9260,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>689885</v>
+        <v>689918</v>
       </c>
       <c r="R82" t="n">
-        <v>6371516</v>
+        <v>6371492</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9308,13 +9322,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944077</t>
+          <t>https://artportalen.se/Sighting/67943938</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>67944085</v>
+        <v>67943995</v>
       </c>
       <c r="B83" t="n">
         <v>87346</v>
@@ -9351,10 +9365,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>689904</v>
+        <v>689894</v>
       </c>
       <c r="R83" t="n">
-        <v>6371549</v>
+        <v>6371499</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9413,13 +9427,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944085</t>
+          <t>https://artportalen.se/Sighting/67943995</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>67944104</v>
+        <v>67944077</v>
       </c>
       <c r="B84" t="n">
         <v>87346</v>
@@ -9456,10 +9470,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>689947</v>
+        <v>689885</v>
       </c>
       <c r="R84" t="n">
-        <v>6371552</v>
+        <v>6371516</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9518,13 +9532,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944104</t>
+          <t>https://artportalen.se/Sighting/67944077</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>67944132</v>
+        <v>67944085</v>
       </c>
       <c r="B85" t="n">
         <v>87346</v>
@@ -9561,10 +9575,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>689923</v>
+        <v>689904</v>
       </c>
       <c r="R85" t="n">
-        <v>6371580</v>
+        <v>6371549</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9623,13 +9637,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944132</t>
+          <t>https://artportalen.se/Sighting/67944085</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>67944195</v>
+        <v>67944104</v>
       </c>
       <c r="B86" t="n">
         <v>87346</v>
@@ -9666,10 +9680,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>689957</v>
+        <v>689947</v>
       </c>
       <c r="R86" t="n">
-        <v>6371614</v>
+        <v>6371552</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9728,13 +9742,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944195</t>
+          <t>https://artportalen.se/Sighting/67944104</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>67944328</v>
+        <v>67944132</v>
       </c>
       <c r="B87" t="n">
         <v>87346</v>
@@ -9771,10 +9785,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>689884</v>
+        <v>689923</v>
       </c>
       <c r="R87" t="n">
-        <v>6371592</v>
+        <v>6371580</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9833,13 +9847,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944328</t>
+          <t>https://artportalen.se/Sighting/67944132</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>67944461</v>
+        <v>67944195</v>
       </c>
       <c r="B88" t="n">
         <v>87346</v>
@@ -9876,10 +9890,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>689927</v>
+        <v>689957</v>
       </c>
       <c r="R88" t="n">
-        <v>6371620</v>
+        <v>6371614</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9938,13 +9952,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67944461</t>
+          <t>https://artportalen.se/Sighting/67944195</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>67945982</v>
+        <v>67944328</v>
       </c>
       <c r="B89" t="n">
         <v>87346</v>
@@ -9981,10 +9995,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>689910</v>
+        <v>689884</v>
       </c>
       <c r="R89" t="n">
-        <v>6371636</v>
+        <v>6371592</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10043,13 +10057,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67945982</t>
+          <t>https://artportalen.se/Sighting/67944328</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>67947062</v>
+        <v>67944461</v>
       </c>
       <c r="B90" t="n">
         <v>87346</v>
@@ -10086,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>689862</v>
+        <v>689927</v>
       </c>
       <c r="R90" t="n">
-        <v>6371574</v>
+        <v>6371620</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10148,13 +10162,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947062</t>
+          <t>https://artportalen.se/Sighting/67944461</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>67947149</v>
+        <v>67945982</v>
       </c>
       <c r="B91" t="n">
         <v>87346</v>
@@ -10191,10 +10205,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>689810</v>
+        <v>689910</v>
       </c>
       <c r="R91" t="n">
-        <v>6371685</v>
+        <v>6371636</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10253,16 +10267,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67947149</t>
+          <t>https://artportalen.se/Sighting/67945982</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>137250770</v>
+        <v>67947062</v>
       </c>
       <c r="B92" t="n">
-        <v>87556</v>
+        <v>87346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10290,20 +10304,19 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>L.mafrids, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>689930</v>
+        <v>689862</v>
       </c>
       <c r="R92" t="n">
-        <v>6371559</v>
+        <v>6371574</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10327,22 +10340,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10358,27 +10361,27 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250770</t>
+          <t>https://artportalen.se/Sighting/67947062</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>137250772</v>
+        <v>67947149</v>
       </c>
       <c r="B93" t="n">
-        <v>87556</v>
+        <v>87346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10406,17 +10409,16 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>L.mafrids, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>689890</v>
+        <v>689810</v>
       </c>
       <c r="R93" t="n">
-        <v>6371658</v>
+        <v>6371685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10443,22 +10445,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:35</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:35</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10474,24 +10466,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250772</t>
+          <t>https://artportalen.se/Sighting/67947149</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137250835</v>
+        <v>137250770</v>
       </c>
       <c r="B94" t="n">
         <v>87556</v>
@@ -10520,19 +10512,22 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Västergarn, Gtl</t>
+          <t>L.mafrids, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>689788</v>
+        <v>689930</v>
       </c>
       <c r="R94" t="n">
-        <v>6371728</v>
+        <v>6371559</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10561,7 +10556,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10571,7 +10566,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10587,24 +10582,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250835</t>
+          <t>https://artportalen.se/Sighting/137250770</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137252240</v>
+        <v>137250772</v>
       </c>
       <c r="B95" t="n">
         <v>87556</v>
@@ -10633,19 +10628,22 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>L.mafrids, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>689870</v>
+        <v>689890</v>
       </c>
       <c r="R95" t="n">
-        <v>6371553</v>
+        <v>6371658</v>
       </c>
       <c r="S95" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10674,7 +10672,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10684,7 +10682,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10700,24 +10698,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137252240</t>
+          <t>https://artportalen.se/Sighting/137250772</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137252241</v>
+        <v>137250835</v>
       </c>
       <c r="B96" t="n">
         <v>87556</v>
@@ -10748,17 +10746,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mosshagen, Gtl</t>
+          <t>Västergarn, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>689850</v>
+        <v>689788</v>
       </c>
       <c r="R96" t="n">
-        <v>6371581</v>
+        <v>6371728</v>
       </c>
       <c r="S96" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10787,7 +10785,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10797,7 +10795,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10813,24 +10811,24 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137252241</t>
+          <t>https://artportalen.se/Sighting/137250835</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137252244</v>
+        <v>137252240</v>
       </c>
       <c r="B97" t="n">
         <v>87556</v>
@@ -10865,13 +10863,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>689707</v>
+        <v>689870</v>
       </c>
       <c r="R97" t="n">
-        <v>6371692</v>
+        <v>6371553</v>
       </c>
       <c r="S97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10900,7 +10898,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10910,7 +10908,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10937,13 +10935,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137252244</t>
+          <t>https://artportalen.se/Sighting/137252240</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137252245</v>
+        <v>137252241</v>
       </c>
       <c r="B98" t="n">
         <v>87556</v>
@@ -10978,13 +10976,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>689816</v>
+        <v>689850</v>
       </c>
       <c r="R98" t="n">
-        <v>6371621</v>
+        <v>6371581</v>
       </c>
       <c r="S98" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11013,7 +11011,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11023,7 +11021,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11050,13 +11048,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137252245</t>
+          <t>https://artportalen.se/Sighting/137252241</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137253829</v>
+        <v>137252244</v>
       </c>
       <c r="B99" t="n">
         <v>87556</v>
@@ -11087,17 +11085,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Västergarn, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>689998</v>
+        <v>689707</v>
       </c>
       <c r="R99" t="n">
-        <v>6371544</v>
+        <v>6371692</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11126,7 +11124,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11136,7 +11134,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11145,30 +11143,31 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137253829</t>
+          <t>https://artportalen.se/Sighting/137252244</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137253833</v>
+        <v>137252245</v>
       </c>
       <c r="B100" t="n">
         <v>87556</v>
@@ -11199,17 +11198,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Västergarn, Gtl</t>
+          <t>Mosshagen, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>689970</v>
+        <v>689816</v>
       </c>
       <c r="R100" t="n">
-        <v>6371614</v>
+        <v>6371621</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11238,7 +11237,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11248,7 +11247,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11257,30 +11256,31 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137253833</t>
+          <t>https://artportalen.se/Sighting/137252245</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137253835</v>
+        <v>137253829</v>
       </c>
       <c r="B101" t="n">
         <v>87556</v>
@@ -11315,13 +11315,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>689937</v>
+        <v>689998</v>
       </c>
       <c r="R101" t="n">
-        <v>6371596</v>
+        <v>6371544</v>
       </c>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11386,13 +11386,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137253835</t>
+          <t>https://artportalen.se/Sighting/137253829</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137253839</v>
+        <v>137253833</v>
       </c>
       <c r="B102" t="n">
         <v>87556</v>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>689918</v>
+        <v>689970</v>
       </c>
       <c r="R102" t="n">
-        <v>6371587</v>
+        <v>6371614</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11497,6 +11497,230 @@
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137253833</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>137253835</v>
+      </c>
+      <c r="B103" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>689937</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6371596</v>
+      </c>
+      <c r="S103" t="n">
+        <v>12</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137253835</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>137253839</v>
+      </c>
+      <c r="B104" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Västergarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>689918</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6371587</v>
+      </c>
+      <c r="S104" t="n">
+        <v>6</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Västergarn</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137253839</t>
         </is>
@@ -11605,6 +11829,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87544</v>
+        <v>87547</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90882</v>
+        <v>90885</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87547</v>
+        <v>87557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90885</v>
+        <v>90895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90895</v>
+        <v>90896</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87558</v>
+        <v>87561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90896</v>
+        <v>90899</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87561</v>
+        <v>87566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90899</v>
+        <v>90904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87566</v>
+        <v>87577</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90904</v>
+        <v>90915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87577</v>
+        <v>87578</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90915</v>
+        <v>90916</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90916</v>
+        <v>90919</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>137252242</v>
       </c>
       <c r="B18" t="n">
-        <v>87581</v>
+        <v>87585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137250773</v>
       </c>
       <c r="B22" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>137250774</v>
       </c>
       <c r="B34" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>137252239</v>
       </c>
       <c r="B35" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>137253832</v>
       </c>
       <c r="B36" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>137250828</v>
       </c>
       <c r="B47" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>137250830</v>
       </c>
       <c r="B48" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>137250832</v>
       </c>
       <c r="B49" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>137250834</v>
       </c>
       <c r="B50" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137253830</v>
       </c>
       <c r="B51" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>137253831</v>
       </c>
       <c r="B52" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137253837</v>
       </c>
       <c r="B53" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>137273810</v>
       </c>
       <c r="B54" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>137273811</v>
       </c>
       <c r="B55" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>137250829</v>
       </c>
       <c r="B60" t="n">
-        <v>90919</v>
+        <v>90923</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>137250833</v>
       </c>
       <c r="B61" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>137250771</v>
       </c>
       <c r="B79" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137250831</v>
       </c>
       <c r="B80" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137252243</v>
       </c>
       <c r="B81" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>137250770</v>
       </c>
       <c r="B94" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>137250772</v>
       </c>
       <c r="B95" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>137250835</v>
       </c>
       <c r="B96" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137252240</v>
       </c>
       <c r="B97" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>137252241</v>
       </c>
       <c r="B98" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>137252244</v>
       </c>
       <c r="B99" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>137252245</v>
       </c>
       <c r="B100" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>137253829</v>
       </c>
       <c r="B101" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>137253833</v>
       </c>
       <c r="B102" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>137253835</v>
       </c>
       <c r="B103" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>137253839</v>
       </c>
       <c r="B104" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
